--- a/NECP Scenario/Results/Regional Results/EL30_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL30_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547329230662118E-12</v>
+        <v>2.284570331009713E-12</v>
       </c>
       <c r="C2">
-        <v>8.102417527459845E-13</v>
+        <v>1.196288306497253E-12</v>
       </c>
       <c r="D2">
-        <v>1.19047921569618E-12</v>
+        <v>1.757696838697942E-12</v>
       </c>
       <c r="E2">
-        <v>1.749241514555178E-12</v>
+        <v>2.582687942973704E-12</v>
       </c>
       <c r="F2">
-        <v>2.570235337680477E-12</v>
+        <v>3.794852388001411E-12</v>
       </c>
       <c r="G2">
-        <v>3.776476431799279E-12</v>
+        <v>5.575819685350622E-12</v>
       </c>
       <c r="H2">
-        <v>2.288789330462262E-11</v>
+        <v>3.379318914221705E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.814656412395772E-08</v>
+        <v>8.932689429116517E-08</v>
       </c>
       <c r="C3">
-        <v>5.184152733293324E-08</v>
+        <v>8.306042023461273E-08</v>
       </c>
       <c r="D3">
-        <v>1.523106689438064E-07</v>
+        <v>2.484450407050784E-07</v>
       </c>
       <c r="E3">
-        <v>0.1811346522031285</v>
+        <v>0.09464232919556885</v>
       </c>
       <c r="F3">
-        <v>0.3325375330461953</v>
+        <v>0.1764570081653319</v>
       </c>
       <c r="G3">
-        <v>0.4475286027221833</v>
+        <v>0.2331471567091782</v>
       </c>
       <c r="H3">
-        <v>0.3631964506864106</v>
+        <v>0.5624186076589315</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.942457951026651E-08</v>
+        <v>7.592786015119654E-08</v>
       </c>
       <c r="C4">
-        <v>4.406529824142911E-08</v>
+        <v>7.060135720564546E-08</v>
       </c>
       <c r="D4">
-        <v>1.29464068610726E-07</v>
+        <v>2.111782846055839E-07</v>
       </c>
       <c r="E4">
-        <v>0.1539644543730662</v>
+        <v>0.08044597981613028</v>
       </c>
       <c r="F4">
-        <v>0.2826569030891138</v>
+        <v>0.1499884569405043</v>
       </c>
       <c r="G4">
-        <v>0.3803993123143074</v>
+        <v>0.1981750832028277</v>
       </c>
       <c r="H4">
-        <v>0.3087169830834994</v>
+        <v>0.478055816510099</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.206429074651132E-12</v>
+        <v>8.989604718579886E-13</v>
       </c>
       <c r="D5">
-        <v>1.207544070590209E-12</v>
+        <v>8.994335272446716E-13</v>
       </c>
       <c r="E5">
-        <v>1.211907983294195E-12</v>
+        <v>9.024682979337041E-13</v>
       </c>
       <c r="F5">
-        <v>1.215833666731466E-12</v>
+        <v>9.052624724851751E-13</v>
       </c>
       <c r="G5">
-        <v>1.220218638812308E-12</v>
+        <v>9.084397064440104E-13</v>
       </c>
       <c r="H5">
-        <v>1.227001852945795E-12</v>
+        <v>9.134210394375992E-13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.1888416667768207</v>
+        <v>0.1888416667550066</v>
       </c>
       <c r="C7">
-        <v>0.1789583334523939</v>
+        <v>0.1789583334379503</v>
       </c>
       <c r="D7">
-        <v>0.1542500000851689</v>
+        <v>0.1542500000656804</v>
       </c>
       <c r="E7">
-        <v>0.1540416667411351</v>
+        <v>0.15404166672021</v>
       </c>
       <c r="F7">
-        <v>0.1538333333975655</v>
+        <v>0.1538333333699465</v>
       </c>
       <c r="G7">
-        <v>0.1531388889255106</v>
+        <v>0.1531388888866608</v>
       </c>
       <c r="H7">
-        <v>0.1524444439679071</v>
+        <v>0.1524444437218532</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.06602855481334295</v>
+        <v>0.06602855480394441</v>
       </c>
       <c r="C9">
-        <v>0.06257284386131808</v>
+        <v>0.06257284385564882</v>
       </c>
       <c r="D9">
-        <v>0.05393356645927454</v>
+        <v>0.05393356645140407</v>
       </c>
       <c r="E9">
-        <v>0.05386072263134138</v>
+        <v>0.05386072262232718</v>
       </c>
       <c r="F9">
-        <v>0.05378787880293977</v>
+        <v>0.05378787879064416</v>
       </c>
       <c r="G9">
-        <v>0.05354506604756466</v>
+        <v>0.05354506602995961</v>
       </c>
       <c r="H9">
-        <v>0.05330225307931216</v>
+        <v>0.05330225296735119</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.122107741746457E-07</v>
+        <v>2.197431785997027E-07</v>
       </c>
       <c r="D10">
-        <v>1.042461482265469E-07</v>
+        <v>2.07196762802663E-07</v>
       </c>
       <c r="E10">
-        <v>1.223496188948171E-07</v>
+        <v>1.785950535996893E-07</v>
       </c>
       <c r="F10">
-        <v>1.059128407799599E-07</v>
+        <v>1.545618389401075E-07</v>
       </c>
       <c r="G10">
-        <v>9.907364768660761E-08</v>
+        <v>1.444489240984864E-07</v>
       </c>
       <c r="H10">
-        <v>3.774617700446417E-07</v>
+        <v>5.614723572530034E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -771,25 +771,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.468117789318938</v>
+        <v>2.47613938032729</v>
       </c>
       <c r="C11">
-        <v>2.645574925569281</v>
+        <v>2.626532525088188</v>
       </c>
       <c r="D11">
-        <v>2.631846927572083</v>
+        <v>2.636402217072559</v>
       </c>
       <c r="E11">
-        <v>1.043489338556608</v>
+        <v>1.055229208080087</v>
       </c>
       <c r="F11">
-        <v>6.628088383936211E-08</v>
+        <v>9.806123440051145E-08</v>
       </c>
       <c r="G11">
-        <v>6.471857284901549E-08</v>
+        <v>9.641843287105982E-08</v>
       </c>
       <c r="H11">
-        <v>3.777165433577216E-07</v>
+        <v>5.615437007929583E-07</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>16.88926754294605</v>
+        <v>16.88926754533713</v>
       </c>
       <c r="C14">
-        <v>17.15575694753577</v>
+        <v>17.15575694544357</v>
       </c>
       <c r="D14">
-        <v>18.85181154071316</v>
+        <v>18.85181152852813</v>
       </c>
       <c r="E14">
-        <v>21.73182869521234</v>
+        <v>21.13899221889011</v>
       </c>
       <c r="F14">
-        <v>26.44994422717128</v>
+        <v>25.85710776046795</v>
       </c>
       <c r="G14">
-        <v>30.46377798456508</v>
+        <v>29.9488886263456</v>
       </c>
       <c r="H14">
-        <v>35.90616856474065</v>
+        <v>35.90616879138923</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5.247219912406845E-08</v>
+        <v>8.887099917506158E-08</v>
       </c>
       <c r="C19">
-        <v>5.15898097468873E-08</v>
+        <v>8.919983900366482E-08</v>
       </c>
       <c r="D19">
-        <v>1.202413759115783E-07</v>
+        <v>2.252846375414722E-07</v>
       </c>
       <c r="E19">
-        <v>0.1096912192838523</v>
+        <v>0.03846327635971698</v>
       </c>
       <c r="F19">
-        <v>0.1222202776204034</v>
+        <v>0.04294511632842275</v>
       </c>
       <c r="G19">
-        <v>0.1325037520722363</v>
+        <v>0.0469676105305867</v>
       </c>
       <c r="H19">
-        <v>0.1291287819268642</v>
+        <v>0.04657544931400541</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4.197775931993409E-08</v>
+        <v>7.109679935967645E-08</v>
       </c>
       <c r="C21">
-        <v>4.127184779750986E-08</v>
+        <v>7.135987120293186E-08</v>
       </c>
       <c r="D21">
-        <v>9.619310072926269E-08</v>
+        <v>1.802277100331777E-07</v>
       </c>
       <c r="E21">
-        <v>0.08775297542723351</v>
+        <v>0.03077062108772913</v>
       </c>
       <c r="F21">
-        <v>0.09777622209632539</v>
+        <v>0.03435609306275651</v>
       </c>
       <c r="G21">
-        <v>0.1060030016578986</v>
+        <v>0.03757408842444104</v>
       </c>
       <c r="H21">
-        <v>0.1033030255414788</v>
+        <v>0.03726035945120373</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>5.079823657022895</v>
+        <v>5.095105808884022</v>
       </c>
       <c r="C24">
-        <v>5.417569648746471</v>
+        <v>5.38114538240459</v>
       </c>
       <c r="D24">
-        <v>5.392081633953509</v>
+        <v>5.400123321264298</v>
       </c>
       <c r="E24">
-        <v>1.982629955687687</v>
+        <v>2.00493580554409</v>
       </c>
       <c r="F24">
-        <v>3.118027100689351E-07</v>
+        <v>4.577546861265813E-07</v>
       </c>
       <c r="G24">
-        <v>2.997214338323322E-07</v>
+        <v>4.411796899543424E-07</v>
       </c>
       <c r="H24">
-        <v>1.411542910600418E-06</v>
+        <v>2.098557417044625E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.556212668285519E-09</v>
+        <v>3.742789670244504E-09</v>
       </c>
       <c r="C25">
-        <v>2.225926638730574E-09</v>
+        <v>3.218904036550531E-09</v>
       </c>
       <c r="D25">
-        <v>2.604955112631408E-09</v>
+        <v>3.811212709601394E-09</v>
       </c>
       <c r="E25">
-        <v>3.342194776980276E-09</v>
+        <v>4.915952552581193E-09</v>
       </c>
       <c r="F25">
-        <v>3.97679588515796E-09</v>
+        <v>5.87280325859596E-09</v>
       </c>
       <c r="G25">
-        <v>4.748264731730821E-09</v>
+        <v>7.021229292391178E-09</v>
       </c>
       <c r="H25">
-        <v>2.673757112426852E-08</v>
+        <v>3.958668736884001E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.52919385381958E-08</v>
+        <v>1.851158195067822E-08</v>
       </c>
       <c r="D27">
-        <v>6.626648489737243E-08</v>
+        <v>6.932386451534582E-08</v>
       </c>
       <c r="E27">
-        <v>8.797009164349237E-08</v>
+        <v>1.116142640723288E-07</v>
       </c>
       <c r="F27">
-        <v>1.865370726543338E-06</v>
+        <v>8.507125970589386E-07</v>
       </c>
       <c r="G27">
-        <v>0.6863359212876623</v>
+        <v>0.4491636477940046</v>
       </c>
       <c r="H27">
-        <v>2.950366101078125</v>
+        <v>2.091946721004237</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>4.432043657581208E-08</v>
+        <v>4.557111678295831E-08</v>
       </c>
       <c r="D30">
-        <v>0.02795319575150131</v>
+        <v>8.918051365828513E-07</v>
       </c>
       <c r="E30">
-        <v>0.109242088994963</v>
+        <v>0.01372282892430176</v>
       </c>
       <c r="F30">
-        <v>0.428466813560875</v>
+        <v>0.3808537129630257</v>
       </c>
       <c r="G30">
-        <v>0.8351735438308538</v>
+        <v>0.8351633929347653</v>
       </c>
       <c r="H30">
-        <v>0.8351703136891563</v>
+        <v>0.8351669636425532</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.3352705729059873</v>
+        <v>0.3352701201492681</v>
       </c>
       <c r="C31">
-        <v>0.33527079464419</v>
+        <v>0.3352705584050325</v>
       </c>
       <c r="D31">
-        <v>0.335264611407374</v>
+        <v>0.3352701561769896</v>
       </c>
       <c r="E31">
-        <v>0.3352696662167215</v>
+        <v>0.3352690033808488</v>
       </c>
       <c r="F31">
-        <v>0.335269378012038</v>
+        <v>0.3352685072314588</v>
       </c>
       <c r="G31">
-        <v>0.3352692520070429</v>
+        <v>0.3352630627494665</v>
       </c>
       <c r="H31">
-        <v>0.3352660706404592</v>
+        <v>0.335262807542437</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>6.622555902686369E-09</v>
+        <v>1.074512313118838E-08</v>
       </c>
       <c r="D32">
-        <v>2.053819084415823E-08</v>
+        <v>3.771956562849044E-08</v>
       </c>
       <c r="E32">
-        <v>0.75879092047112</v>
+        <v>1.35162740485447</v>
       </c>
       <c r="F32">
-        <v>0.7587909108917129</v>
+        <v>1.35162739022292</v>
       </c>
       <c r="G32">
-        <v>1.771446265066039</v>
+        <v>2.286335642499633</v>
       </c>
       <c r="H32">
-        <v>4.408443220715418</v>
+        <v>4.408443106821202</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.05148788346394725</v>
+        <v>0.05148788103963114</v>
       </c>
       <c r="C33">
-        <v>0.05148788428137572</v>
+        <v>0.05148788208792033</v>
       </c>
       <c r="D33">
-        <v>0.05148787816867119</v>
+        <v>0.0514878732792946</v>
       </c>
       <c r="E33">
-        <v>0.05148787296262977</v>
+        <v>0.05148786533307692</v>
       </c>
       <c r="F33">
-        <v>0.05148786285916029</v>
+        <v>0.05148785002667919</v>
       </c>
       <c r="G33">
-        <v>0.0514878462885618</v>
+        <v>0.05148782696264326</v>
       </c>
       <c r="H33">
-        <v>0.05148764829567028</v>
+        <v>0.05148753575549492</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>1.643351518571493E-08</v>
+        <v>2.553855214000534E-08</v>
       </c>
       <c r="D34">
-        <v>1.954317388349298E-08</v>
+        <v>3.033191765569801E-08</v>
       </c>
       <c r="E34">
-        <v>3.855507770341787E-08</v>
+        <v>5.36243102130718E-08</v>
       </c>
       <c r="F34">
-        <v>5.82627612078345E-08</v>
+        <v>8.476534275318194E-08</v>
       </c>
       <c r="G34">
-        <v>7.857049650330421E-08</v>
+        <v>1.127879960071166E-07</v>
       </c>
       <c r="H34">
-        <v>4.781620779994262E-07</v>
+        <v>7.186059197990151E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.001616990330151064</v>
+        <v>0.00161695871523265</v>
       </c>
       <c r="C35">
-        <v>0.001616995529462763</v>
+        <v>0.001616983887914392</v>
       </c>
       <c r="D35">
-        <v>0.001616992326924705</v>
+        <v>0.001616971660655494</v>
       </c>
       <c r="E35">
-        <v>0.001616933061349657</v>
+        <v>0.001616763303668105</v>
       </c>
       <c r="F35">
-        <v>0.001616952079299701</v>
+        <v>0.001616817835129537</v>
       </c>
       <c r="G35">
-        <v>0.00161694185775747</v>
+        <v>0.001616754170835431</v>
       </c>
       <c r="H35">
-        <v>0.001616552186173353</v>
+        <v>0.001616697837063136</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>3.082737448977439E-07</v>
+        <v>1.333681356069999E-07</v>
       </c>
       <c r="D36">
-        <v>2.997374425577387E-07</v>
+        <v>1.481464023902366E-07</v>
       </c>
       <c r="E36">
-        <v>2.297212667455023E-07</v>
+        <v>1.474785951851603E-07</v>
       </c>
       <c r="F36">
-        <v>6.122341820182136E-07</v>
+        <v>6.684346142311643E-07</v>
       </c>
       <c r="G36">
-        <v>6.01123977321817E-07</v>
+        <v>6.755692958892989E-07</v>
       </c>
       <c r="H36">
-        <v>1.535166613904896E-06</v>
+        <v>2.238771419205037E-06</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1.786512385280813</v>
+        <v>1.717299817943009</v>
       </c>
       <c r="C37">
-        <v>1.758121653023597</v>
+        <v>1.688208995626385</v>
       </c>
       <c r="D37">
-        <v>1.672413176882534</v>
+        <v>1.616161261413117</v>
       </c>
       <c r="E37">
-        <v>1.293427819723947</v>
+        <v>1.285026351306198</v>
       </c>
       <c r="F37">
-        <v>1.499165598981021</v>
+        <v>1.503117038175021</v>
       </c>
       <c r="G37">
-        <v>1.759362818644744</v>
+        <v>1.671873299221091</v>
       </c>
       <c r="H37">
-        <v>1.902719060221926</v>
+        <v>1.898671110724383</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.1162538268044495</v>
+        <v>0.1854668809382062</v>
       </c>
       <c r="C38">
-        <v>0.1446444037856655</v>
+        <v>0.2145573068675112</v>
       </c>
       <c r="D38">
-        <v>0.2303653790484257</v>
+        <v>0.2866056587514038</v>
       </c>
       <c r="E38">
-        <v>0.6093409959537089</v>
+        <v>0.6177438344866489</v>
       </c>
       <c r="F38">
-        <v>0.4036047296593205</v>
+        <v>0.3996547255560495</v>
       </c>
       <c r="G38">
-        <v>0.5798795024594614</v>
+        <v>0.5484854166974752</v>
       </c>
       <c r="H38">
-        <v>0.946774600006666</v>
+        <v>0.7678761760013542</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1.106187632480262E-07</v>
+        <v>1.781978934662268E-07</v>
       </c>
       <c r="C40">
-        <v>1.034313370798205E-07</v>
+        <v>1.722602592382775E-07</v>
       </c>
       <c r="D40">
-        <v>2.725520448553847E-07</v>
+        <v>4.737296782465505E-07</v>
       </c>
       <c r="E40">
-        <v>0.2908258714869808</v>
+        <v>0.1331056055552858</v>
       </c>
       <c r="F40">
-        <v>0.4547578106665988</v>
+        <v>0.2194021244937547</v>
       </c>
       <c r="G40">
-        <v>0.5800323547944196</v>
+        <v>0.2801147672397649</v>
       </c>
       <c r="H40">
-        <v>0.4923252326132748</v>
+        <v>0.6089940569729368</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>9.14023388302006E-08</v>
+        <v>1.47024659510873E-07</v>
       </c>
       <c r="C41">
-        <v>8.533714603893897E-08</v>
+        <v>1.419612284085773E-07</v>
       </c>
       <c r="D41">
-        <v>2.256571693399887E-07</v>
+        <v>3.914059946387616E-07</v>
       </c>
       <c r="E41">
-        <v>0.2417174298002998</v>
+        <v>0.1112166009038594</v>
       </c>
       <c r="F41">
-        <v>0.3804331251854393</v>
+        <v>0.1843445500032608</v>
       </c>
       <c r="G41">
-        <v>0.486402313972206</v>
+        <v>0.2357491716272688</v>
       </c>
       <c r="H41">
-        <v>0.4120200086249782</v>
+        <v>0.5153161759613027</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-1.921642441782556E-08</v>
+        <v>-3.117323395535375E-08</v>
       </c>
       <c r="C42">
-        <v>-1.809419104088158E-08</v>
+        <v>-3.029903082970022E-08</v>
       </c>
       <c r="D42">
-        <v>-4.689487551539601E-08</v>
+        <v>-8.232368360778889E-08</v>
       </c>
       <c r="E42">
-        <v>-0.04910844168668105</v>
+        <v>-0.02188900465142643</v>
       </c>
       <c r="F42">
-        <v>-0.0743246854811595</v>
+        <v>-0.03505757449049385</v>
       </c>
       <c r="G42">
-        <v>-0.0936300408222136</v>
+        <v>-0.04436559561249609</v>
       </c>
       <c r="H42">
-        <v>-0.08030522398829654</v>
+        <v>-0.0936778810116341</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>12.57640019627416</v>
+        <v>12.63759167044229</v>
       </c>
       <c r="C43">
-        <v>12.7027167408416</v>
+        <v>12.79167211168975</v>
       </c>
       <c r="D43">
-        <v>14.51351347075987</v>
+        <v>14.59315693519782</v>
       </c>
       <c r="E43">
-        <v>19.38753679304304</v>
+        <v>18.84756385431832</v>
       </c>
       <c r="F43">
-        <v>24.74575435817478</v>
+        <v>24.14521559431639</v>
       </c>
       <c r="G43">
-        <v>27.5078133874537</v>
+        <v>27.25782977166445</v>
       </c>
       <c r="H43">
-        <v>30.64080959333431</v>
+        <v>31.51665495437051</v>
       </c>
     </row>
     <row r="44" spans="1:8">
